--- a/test1_converted.xlsx
+++ b/test1_converted.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Live Allownace</t>
+          <t>Live Allowance</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
